--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,6 +919,131 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127908235</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56585</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Välsviksleden 218, 656 31 Karlstad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>419196</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6584351</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>127908235</v>
       </c>
       <c r="B4" t="n">
-        <v>56585</v>
+        <v>56612</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>127908235</v>
       </c>
       <c r="B4" t="n">
-        <v>56612</v>
+        <v>56615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>127908235</v>
       </c>
       <c r="B4" t="n">
-        <v>56615</v>
+        <v>56618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>127908235</v>
       </c>
       <c r="B4" t="n">
-        <v>56618</v>
+        <v>56620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,6 +1044,126 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129642494</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58444</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Välsviken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>419497</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6584277</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Karlstads Kommun - Kroppkärrsjön Fågelinventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>129642494</v>
       </c>
       <c r="B5" t="n">
-        <v>58444</v>
+        <v>58447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>129642494</v>
       </c>
       <c r="B5" t="n">
-        <v>58447</v>
+        <v>58452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>129642494</v>
       </c>
       <c r="B5" t="n">
-        <v>58452</v>
+        <v>58453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>129642494</v>
       </c>
       <c r="B5" t="n">
-        <v>58453</v>
+        <v>58456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>129642494</v>
       </c>
       <c r="B5" t="n">
-        <v>58456</v>
+        <v>58459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57624134</v>
+        <v>101450618</v>
       </c>
       <c r="B2" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57719</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>100018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Rördrom</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Botaurus stellaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,34 +708,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alstersnäset, NV delen, Vrm</t>
+          <t>Frödingleden/cykelvägen Välsviken, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419499.0336990892</v>
+        <v>419437</v>
       </c>
       <c r="R2" t="n">
-        <v>6584129.864337007</v>
+        <v>6584253</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-05-22</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-09-16</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,27 +782,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olof Persson</t>
+          <t>Magnus Köpman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olof Persson, Tomas Fasth</t>
+          <t>Magnus Köpman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113905071</v>
+        <v>57624134</v>
       </c>
       <c r="B3" t="n">
-        <v>57271</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,24 +827,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Välsviken, Vrm</t>
+          <t>Alstersnäset, NV delen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419465</v>
+        <v>419499</v>
       </c>
       <c r="R3" t="n">
-        <v>6584423</v>
+        <v>6584130</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,12 +878,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2015-05-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2015-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,26 +898,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Olof Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Karlstads kommun - NVI Reningsverk</t>
-        </is>
-      </c>
+          <t>Olof Persson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127908235</v>
+        <v>113905071</v>
       </c>
       <c r="B4" t="n">
-        <v>56620</v>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100053</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,29 +943,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Välsviksleden 218, 656 31 Karlstad, Vrm</t>
+          <t>Välsviken, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419196</v>
+        <v>419465</v>
       </c>
       <c r="R4" t="n">
-        <v>6584351</v>
+        <v>6584423</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,22 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,73 +1004,69 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+          <t>Karlstads kommun - NVI Reningsverk</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129642494</v>
+        <v>132602217</v>
       </c>
       <c r="B5" t="n">
-        <v>58459</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Välsviken, Vrm</t>
+          <t>Välsviksområdet, Karlstadsområdet, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419497</v>
+        <v>419439</v>
       </c>
       <c r="R5" t="n">
-        <v>6584277</v>
+        <v>6584180</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,22 +1090,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,23 +1116,1383 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Camilla Berglund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Camilla Berglund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127908235</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56845</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Välsviksleden 218, 656 31 Karlstad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>419196</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6584351</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>107631987</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2K+</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Frödingleden/cykelvägen Välsviken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>419437</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6584253</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-03-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-03-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Drog mot NW.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Köpman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Köpman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121397066</v>
+      </c>
+      <c r="B8" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Välsviken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>419098</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6584317</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Greensway AB</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Tufvesson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Karlstad kommun - Inventering inför områdesskydd 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129642515</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58286</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Välsviktjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>419482</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6584044</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Sara Poppelaars</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t xml:space="preserve"> Karlstads Kommun - Kroppkärrsjön Fågelinventering</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>101450619</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Frödingleden/cykelvägen Välsviken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>419437</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6584253</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>04:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>04:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Granskogen helt skövlad så den har flyttat till strandskogen med  al och Björk.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Köpman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Köpman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113904805</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Alstersnäset, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>419699</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6584387</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-04-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-04-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Karlstads kommun - NVI Reningsverk</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129642494</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Välsviken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>419497</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6584277</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Karlstads Kommun - Kroppkärrsjön Fågelinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129642514</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58649</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103057</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sävsparv</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Emberiza schoeniclus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Välsviktjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>419456</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6584069</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Karlstads Kommun - Kroppkärrsjön Fågelinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>104320888</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Söder om järnvägen intill grusväg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>419198</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6584321</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-07-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>04:13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Åsa Duell, Andreas Mitander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104320920</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Söder om järnvägen intill grusväg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>419198</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6584321</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-07-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>04:13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Åsa Duell, Andreas Mitander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104320881</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Söder om järnvägen intill grusväg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>419198</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6584321</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-07-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>04:13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Åsa Duell, Andreas Mitander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101450618</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57624134</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Karlstads kommun - NVI Reningsverk</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113905071</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1154,6 +1174,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132602217</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1279,6 +1304,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127908235</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1407,6 +1437,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107631987</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1522,6 +1557,11 @@
           <t>Karlstad kommun - Inventering inför områdesskydd 2024</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121397066</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1631,6 +1671,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135068081</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1751,6 +1796,11 @@
           <t xml:space="preserve"> Karlstads Kommun - Kroppkärrsjön Fågelinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129642515</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1875,6 +1925,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101450619</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1990,6 +2045,11 @@
           <t>Karlstads kommun - NVI Reningsverk</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113904805</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2110,6 +2170,11 @@
           <t xml:space="preserve"> Karlstads Kommun - Kroppkärrsjön Fågelinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129642494</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2230,6 +2295,11 @@
           <t xml:space="preserve"> Karlstads Kommun - Kroppkärrsjön Fågelinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129642514</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2354,6 +2424,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320888</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2478,6 +2553,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320920</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2602,8 +2682,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320881</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -1568,7 +1568,7 @@
         <v>135068081</v>
       </c>
       <c r="B9" t="n">
-        <v>58061</v>
+        <v>58066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
